--- a/webconfig/Holocene_Volcanoes_volcdef_cfg.xlsx
+++ b/webconfig/Holocene_Volcanoes_volcdef_cfg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/famelung/code/minsar/webconfig/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D007BBF-D185-984A-9884-C366F8BA3EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB602A0F-2152-9743-BF85-67221C099555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7060" yWindow="2040" windowWidth="29500" windowHeight="19160" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
   </bookViews>
@@ -6020,9 +6020,6 @@
     <t>http://149.165.154.65/data/HDF5EOS/Pichincha/miaplpy/#/start/-0.1724/-78.6050/14.5940?startDataset=S1_desc_040_miaplpy_20141020_XXXXXXXX_S0015W07856_S0013W07863_S0021W07864_S0023W07857_filtDel4DS&amp;minScale=-1.5&amp;maxScale=1.5&amp;pixelSize=5.4&amp;background=satellite</t>
   </si>
   <si>
-    <t>http://149.165.153.50/start/-0.4400/-91.1254/8.9304?flyToDatasetCenter=false&amp;startDataset=S1_desc_128_mintpy_20200104_XXXXXXXX&amp;minScale=-30&amp;maxScale=30</t>
-  </si>
-  <si>
     <t>http://149.165.154.65/data/HDF5EOS/Hawaii/mintpy/</t>
   </si>
   <si>
@@ -6036,6 +6033,9 @@
   </si>
   <si>
     <t>Geothermal</t>
+  </si>
+  <si>
+    <t>http://insarmaps.miami.edu/start/-0.4400/-91.1254/8.9304?flyToDatasetCenter=false&amp;startDataset=S1_desc_128_mintpy_20200104_XXXXXXXX&amp;minScale=-30&amp;maxScale=30</t>
   </si>
 </sst>
 </file>
@@ -46266,13 +46266,13 @@
     </row>
     <row r="905" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="6" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B905" s="3">
         <v>332010</v>
       </c>
       <c r="C905" s="1" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="D905" s="1" t="s">
         <v>446</v>
@@ -46310,19 +46310,19 @@
     </row>
     <row r="906" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="6" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B906" s="3">
         <v>332010</v>
       </c>
       <c r="C906" s="1" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="D906" s="1" t="s">
         <v>446</v>
       </c>
       <c r="E906" s="1" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="F906" s="1" t="s">
         <v>44</v>
@@ -53570,7 +53570,7 @@
     </row>
     <row r="1071" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1071" s="5" t="s">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="B1071" s="3">
         <v>353010</v>

--- a/webconfig/Holocene_Volcanoes_volcdef_cfg.xlsx
+++ b/webconfig/Holocene_Volcanoes_volcdef_cfg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/famelung/code/minsar/webconfig/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB602A0F-2152-9743-BF85-67221C099555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D66059-8D22-8342-8350-30A16FBEC8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7060" yWindow="2040" windowWidth="29500" windowHeight="19160" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
+    <workbookView xWindow="7040" yWindow="660" windowWidth="29500" windowHeight="19160" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/webconfig/Holocene_Volcanoes_volcdef_cfg.xlsx
+++ b/webconfig/Holocene_Volcanoes_volcdef_cfg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/famelung/code/minsar/webconfig/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D66059-8D22-8342-8350-30A16FBEC8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00028CB-775D-A54E-8D7C-1E0165BFCFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7040" yWindow="660" windowWidth="29500" windowHeight="19160" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
   </bookViews>
@@ -5954,9 +5954,6 @@
     <t>q</t>
   </si>
   <si>
-    <t>Galapagaos</t>
-  </si>
-  <si>
     <t>http://149.165.154.65/data/HDF5EOS/Wolf/mintpy/</t>
   </si>
   <si>
@@ -6036,6 +6033,9 @@
   </si>
   <si>
     <t>http://insarmaps.miami.edu/start/-0.4400/-91.1254/8.9304?flyToDatasetCenter=false&amp;startDataset=S1_desc_128_mintpy_20200104_XXXXXXXX&amp;minScale=-30&amp;maxScale=30</t>
+  </si>
+  <si>
+    <t>Galapagos</t>
   </si>
 </sst>
 </file>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B23" s="3">
         <v>212040</v>
@@ -7546,19 +7546,19 @@
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B25" s="3">
         <v>212050</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>1970</v>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B26" s="3">
         <v>212050</v>
@@ -7602,7 +7602,7 @@
         <v>79</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>1970</v>
@@ -7634,19 +7634,19 @@
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B27" s="3">
         <v>212050</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>1970</v>
@@ -7678,19 +7678,19 @@
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B28" s="3">
         <v>212050</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>1970</v>
@@ -7722,19 +7722,19 @@
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B29" s="3">
         <v>212050</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>1970</v>
@@ -46266,13 +46266,13 @@
     </row>
     <row r="905" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="6" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B905" s="3">
         <v>332010</v>
       </c>
       <c r="C905" s="1" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="D905" s="1" t="s">
         <v>446</v>
@@ -46310,19 +46310,19 @@
     </row>
     <row r="906" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="6" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B906" s="3">
         <v>332010</v>
       </c>
       <c r="C906" s="1" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="D906" s="1" t="s">
         <v>446</v>
       </c>
       <c r="E906" s="1" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="F906" s="1" t="s">
         <v>44</v>
@@ -52998,7 +52998,7 @@
     </row>
     <row r="1058" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1058" s="6" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B1058" s="3">
         <v>352020</v>
@@ -53570,13 +53570,13 @@
     </row>
     <row r="1071" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1071" s="5" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B1071" s="3">
         <v>353010</v>
       </c>
       <c r="C1071" s="1" t="s">
-        <v>1972</v>
+        <v>1999</v>
       </c>
       <c r="D1071" s="1" t="s">
         <v>1579</v>
@@ -53614,7 +53614,7 @@
     </row>
     <row r="1072" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1072" s="5" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B1072" s="3">
         <v>353010</v>
@@ -53658,7 +53658,7 @@
     </row>
     <row r="1073" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1073" s="5" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B1073" s="3">
         <v>353010</v>
@@ -53746,7 +53746,7 @@
     </row>
     <row r="1075" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1075" s="6" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B1075" s="3">
         <v>353020</v>
@@ -53834,7 +53834,7 @@
     </row>
     <row r="1077" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1077" s="5" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B1077" s="3">
         <v>353040</v>
@@ -53878,7 +53878,7 @@
     </row>
     <row r="1078" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1078" s="5" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B1078" s="3">
         <v>353050</v>
@@ -53922,7 +53922,7 @@
     </row>
     <row r="1079" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1079" s="6" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B1079" s="3">
         <v>353060</v>
@@ -53966,7 +53966,7 @@
     </row>
     <row r="1080" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1080" s="6" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B1080" s="3">
         <v>353060</v>
@@ -62810,7 +62810,7 @@
     </row>
     <row r="1281" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1281" s="6" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B1281" s="3">
         <v>383010</v>
@@ -63778,7 +63778,7 @@
     </row>
     <row r="1303" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1303" s="1" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B1303" s="3">
         <v>390021</v>
